--- a/WpfApp1/tmp/Book1.xlsx
+++ b/WpfApp1/tmp/Book1.xlsx
@@ -9,11 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27450" windowHeight="11445" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27450" windowHeight="11445"/>
   </bookViews>
   <sheets>
-    <sheet name="swrt_1" sheetId="1" r:id="rId1"/>
-    <sheet name="swrt_2" sheetId="2" r:id="rId2"/>
+    <sheet name="表記フォーマット" sheetId="3" r:id="rId1"/>
+    <sheet name="swrt_1" sheetId="1" r:id="rId2"/>
+    <sheet name="swrt_2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>データ名</t>
     <rPh sb="3" eb="4">
@@ -127,6 +128,78 @@
   </si>
   <si>
     <t>ram8[4].BYTE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>discription</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>placeholder</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dec</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dec_x10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ddd</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ddd.d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16進</t>
+    <rPh sb="2" eb="3">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10進</t>
+    <rPh sb="2" eb="3">
+      <t>シン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10進 10倍値</t>
+    <rPh sb="2" eb="3">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>バイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1bit</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -455,107 +528,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2">
+        <v>28</v>
+      </c>
+      <c r="B2">
         <v>64</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="B3">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>200</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -591,6 +634,117 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
